--- a/pcb/docs/bom/esp32stepper-bom.xlsx
+++ b/pcb/docs/bom/esp32stepper-bom.xlsx
@@ -727,7 +727,7 @@
     <t>BoM Date:</t>
   </si>
   <si>
-    <t>2025-03-27T18:42:32+0000</t>
+    <t>2025-04-03T21:17:37+0000</t>
   </si>
   <si>
     <t>Schematic Source:</t>
@@ -739,7 +739,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>Eeschema 9.0.0</t>
+    <t>Eeschema 9.0.1</t>
   </si>
 </sst>
 </file>
